--- a/Info datos.xlsx
+++ b/Info datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Documents\Github\Clase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AD8DAE-92D9-4970-A4FA-A8A7FA08558A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2165202-B951-46CE-9C4A-6B786E2933D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{40CF7B30-E04F-4EA8-8E69-AF33A4B38F89}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="56">
   <si>
     <t>DCL</t>
   </si>
@@ -195,17 +195,23 @@
     <t>Frecuencia (Hz)</t>
   </si>
   <si>
-    <t>Núm. puntos registrados en documento</t>
-  </si>
-  <si>
-    <t>Núm. puntos vistos en codigo</t>
+    <t>Núm. puntos registrados en excel</t>
+  </si>
+  <si>
+    <t>Tiempo (min)</t>
+  </si>
+  <si>
+    <t>Tiempo (seg)</t>
+  </si>
+  <si>
+    <t>Núm. puntos señal original</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,8 +227,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,8 +266,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -283,25 +302,14 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -331,16 +339,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -358,6 +375,94 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2240</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>6642</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1653268</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>88446</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CuadroTexto 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73D0431B-B516-C485-7EEB-8FF62DA4258E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="791454" y="4973249"/>
+          <a:ext cx="8134832" cy="265501"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100"/>
+            <a:t>Los participantes en rojo,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100"/>
+            <a:t>los primeros 5 min no son los de reposo, hay que revisar de que punto a que punto hacer el recorte</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100" baseline="0"/>
+            <a:t> para ojos cerrados.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-MX" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -677,29 +782,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F50DDF32-117A-4251-BFF4-DB3AD4EA1D60}">
-  <dimension ref="B2:I26"/>
+  <dimension ref="B2:K26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" customWidth="1"/>
     <col min="7" max="7" width="14.21875" customWidth="1"/>
-    <col min="8" max="8" width="34.5546875" customWidth="1"/>
-    <col min="9" max="9" width="27.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="29.77734375" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-    </row>
-    <row r="3" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+    </row>
+    <row r="3" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
         <v>49</v>
       </c>
@@ -715,17 +826,23 @@
       <c r="F3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="11" t="s">
         <v>51</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="K3" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
@@ -742,7 +859,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="4">
-        <v>511.99</v>
+        <v>512</v>
       </c>
       <c r="H4" s="4">
         <v>353117</v>
@@ -750,8 +867,14 @@
       <c r="I4" s="4">
         <v>368475</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="13">
+        <v>0.47847222222222224</v>
+      </c>
+      <c r="K4" s="4">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -768,7 +891,7 @@
         <v>81</v>
       </c>
       <c r="G5" s="4">
-        <v>511.99</v>
+        <v>512</v>
       </c>
       <c r="H5" s="4">
         <v>363148</v>
@@ -776,8 +899,14 @@
       <c r="I5" s="4">
         <v>373386</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J5" s="13">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="K5" s="4">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -802,8 +931,14 @@
       <c r="I6" s="4">
         <v>173927</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J6" s="13">
+        <v>0.59652777777777777</v>
+      </c>
+      <c r="K6" s="4">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
@@ -820,7 +955,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="4">
-        <v>511.99</v>
+        <v>512</v>
       </c>
       <c r="H7" s="4">
         <v>332519</v>
@@ -828,8 +963,14 @@
       <c r="I7" s="4">
         <v>340197</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="13">
+        <v>0.45069444444444445</v>
+      </c>
+      <c r="K7" s="4">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
@@ -845,13 +986,23 @@
       <c r="F8" s="4">
         <v>30</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="G8" s="4">
+        <v>200</v>
+      </c>
+      <c r="H8" s="4">
+        <v>175833</v>
+      </c>
       <c r="I8" s="4">
         <v>175833</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J8" s="13">
+        <v>0.61041666666666672</v>
+      </c>
+      <c r="K8" s="4">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -876,8 +1027,14 @@
       <c r="I9" s="4">
         <v>350809</v>
       </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="13">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="K9" s="4">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
@@ -894,7 +1051,7 @@
         <v>90</v>
       </c>
       <c r="G10" s="4">
-        <v>511.99</v>
+        <v>512</v>
       </c>
       <c r="H10" s="4">
         <v>452516</v>
@@ -902,9 +1059,15 @@
       <c r="I10" s="4">
         <v>460194</v>
       </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="4" t="s">
+      <c r="J10" s="13">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="K10" s="4">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -928,26 +1091,34 @@
       <c r="I11" s="4">
         <v>164954</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J11" s="13">
+        <v>0.56180555555555556</v>
+      </c>
+      <c r="K11" s="4">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>49</v>
       </c>
@@ -970,11 +1141,17 @@
         <v>52</v>
       </c>
       <c r="I14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="4" t="s">
+      <c r="K14" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -989,17 +1166,23 @@
       <c r="F15" s="4">
         <v>117</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="4">
         <v>256</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="4">
         <v>117955</v>
       </c>
       <c r="I15" s="4">
         <v>125634</v>
       </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J15" s="13">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="K15" s="4">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>11</v>
       </c>
@@ -1018,14 +1201,20 @@
       <c r="G16" s="4">
         <v>200</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="4">
         <v>130665</v>
       </c>
       <c r="I16" s="4">
         <v>136664</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J16" s="13">
+        <v>0.45347222222222222</v>
+      </c>
+      <c r="K16" s="4">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
@@ -1041,17 +1230,23 @@
       <c r="F17" s="4">
         <v>110</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="4">
         <v>200</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="4">
         <v>144923</v>
       </c>
       <c r="I17" s="4">
         <v>150922</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J17" s="13">
+        <v>0.50277777777777777</v>
+      </c>
+      <c r="K17" s="4">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>13</v>
       </c>
@@ -1067,17 +1262,23 @@
       <c r="F18" s="4">
         <v>113</v>
       </c>
-      <c r="G18" s="11">
-        <v>511.99</v>
-      </c>
-      <c r="H18" s="11">
+      <c r="G18" s="17">
+        <v>512</v>
+      </c>
+      <c r="H18" s="4">
         <v>369142</v>
       </c>
       <c r="I18" s="4">
         <v>369142</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J18" s="13">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="K18" s="4">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
@@ -1093,17 +1294,23 @@
       <c r="F19" s="4">
         <v>102</v>
       </c>
-      <c r="G19" s="11">
-        <v>511.99</v>
-      </c>
-      <c r="H19" s="11">
+      <c r="G19" s="4">
+        <v>512</v>
+      </c>
+      <c r="H19" s="4">
         <v>357632</v>
       </c>
       <c r="I19" s="4">
         <v>357632</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J19" s="13">
+        <v>0.48472222222222222</v>
+      </c>
+      <c r="K19" s="4">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
@@ -1119,17 +1326,23 @@
       <c r="F20" s="4">
         <v>114</v>
       </c>
-      <c r="G20" s="11">
-        <v>511.99</v>
-      </c>
-      <c r="H20" s="11">
+      <c r="G20" s="4">
+        <v>512</v>
+      </c>
+      <c r="H20" s="4">
         <v>336698</v>
       </c>
       <c r="I20" s="4">
         <v>344376</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J20" s="13">
+        <v>0.45624999999999999</v>
+      </c>
+      <c r="K20" s="4">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>16</v>
       </c>
@@ -1145,17 +1358,23 @@
       <c r="F21" s="4">
         <v>113</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="4">
         <v>512</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="4">
         <v>371378</v>
       </c>
       <c r="I21" s="4">
         <v>379057</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J21" s="13">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="K21" s="4">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>17</v>
       </c>
@@ -1171,18 +1390,24 @@
       <c r="F22" s="4">
         <v>106</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="16">
         <v>512</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="4">
         <v>338865</v>
       </c>
       <c r="I22" s="4">
         <v>338865</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="4" t="s">
+      <c r="J22" s="13">
+        <v>0.43819444444444444</v>
+      </c>
+      <c r="K22" s="4">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="12" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -1200,14 +1425,20 @@
       <c r="G23" s="4">
         <v>200</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="4">
         <v>39589</v>
       </c>
       <c r="I23" s="4">
         <v>42588</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J23" s="13">
+        <v>0.13680555555555557</v>
+      </c>
+      <c r="K23" s="4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>18</v>
       </c>
@@ -1223,27 +1454,34 @@
       <c r="F24" s="4">
         <v>114</v>
       </c>
-      <c r="G24" s="11">
-        <v>512</v>
-      </c>
-      <c r="H24" s="11">
+      <c r="G24" s="4">
+        <v>200</v>
+      </c>
+      <c r="H24" s="4">
         <v>73600</v>
       </c>
       <c r="I24" s="4">
         <v>73600</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J24" s="13">
+        <v>0.25555555555555554</v>
+      </c>
+      <c r="K24" s="4">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B13:K13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
